--- a/JsonConverter/ExcelFiles/Dialogue.xlsx
+++ b/JsonConverter/ExcelFiles/Dialogue.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SunnyHoGaming\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6AFD2C1-0BF2-4453-86A6-9246E4C42F9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D5C1B72-FB9F-4AE7-9B4A-0068CAFC4FEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="615" yWindow="1815" windowWidth="28185" windowHeight="12795" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table_Story" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="31">
   <si>
     <t>Id</t>
   </si>
@@ -46,27 +46,97 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>나만 살아남았다.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>Dialogue_Day1_001</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>여기는 구조대 생존자 있나요?</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dialogue_Day4_002</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>다음 다이얼로그 Id</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>NextId</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Day1_011</t>
+  </si>
+  <si>
+    <t>Dialogue_Day1_012</t>
+  </si>
+  <si>
+    <t>혼자 남게 되었다</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>절망적이지만 나는 살아야만 한다</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>정신차리고 주변을 살펴보자</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Day1_002</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Day1_003</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>산소 공급기 또한 손상되었구나</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>서둘러 수리해보자</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Day1_005</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>정말 핵심 기능들이 많이 손상되었네</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Day1_007</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>탐사선 내부 온도도 불안정하다</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Day1_006</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Day1_004</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>전력이 모두 소진되기전에 수리하자</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>점점 지구와 멀어지고 있었다니</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>서둘러 항로 제어기를 수리하자</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Day1_010</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Day1_008</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Day1_009</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -196,7 +266,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -205,12 +275,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -482,21 +546,21 @@
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="15" t="s">
-        <v>11</v>
+      <c r="C1" s="13" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="13" t="s">
         <v>6</v>
       </c>
     </row>
@@ -504,180 +568,226 @@
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="16" t="s">
-        <v>12</v>
+      <c r="C3" s="14" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15.75" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="17"/>
+      <c r="B4" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="5" spans="1:3" ht="15.75" customHeight="1">
       <c r="A5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A6" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="15"/>
+    </row>
+    <row r="7" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="16"/>
+    </row>
+    <row r="9" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A9" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="17"/>
+    </row>
+    <row r="11" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A11" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="17"/>
+    </row>
+    <row r="12" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A12" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A13" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="15"/>
+    </row>
+    <row r="14" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="17"/>
-    </row>
-    <row r="6" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A6" s="3"/>
-      <c r="B6" s="11"/>
-      <c r="C6" s="17"/>
-    </row>
-    <row r="7" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A7" s="3"/>
-      <c r="B7" s="11"/>
-      <c r="C7" s="17"/>
-    </row>
-    <row r="8" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A8" s="3"/>
-      <c r="B8" s="12"/>
-      <c r="C8" s="18"/>
-    </row>
-    <row r="9" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A9" s="3"/>
-      <c r="B9" s="12"/>
-      <c r="C9" s="18"/>
-    </row>
-    <row r="10" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A10" s="3"/>
-      <c r="B10" s="13"/>
-      <c r="C10" s="19"/>
-    </row>
-    <row r="11" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A11" s="5"/>
-      <c r="B11" s="13"/>
-      <c r="C11" s="19"/>
-    </row>
-    <row r="12" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A12" s="4"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="18"/>
-    </row>
-    <row r="13" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A13" s="3"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="17"/>
-    </row>
-    <row r="14" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A14" s="5"/>
-      <c r="B14" s="13"/>
-      <c r="C14" s="19"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="17"/>
     </row>
     <row r="15" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A15" s="5"/>
-      <c r="B15" s="13"/>
-      <c r="C15" s="19"/>
+      <c r="A15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" s="11"/>
+      <c r="C15" s="17"/>
     </row>
     <row r="16" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A16" s="6"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="20"/>
+      <c r="A16" s="4"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="18"/>
     </row>
     <row r="17" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A17" s="6"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="20"/>
+      <c r="A17" s="4"/>
+      <c r="B17" s="12"/>
+      <c r="C17" s="18"/>
     </row>
     <row r="18" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A18" s="6"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="20"/>
+      <c r="A18" s="4"/>
+      <c r="B18" s="12"/>
+      <c r="C18" s="18"/>
     </row>
     <row r="19" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A19" s="6"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="20"/>
+      <c r="A19" s="4"/>
+      <c r="B19" s="12"/>
+      <c r="C19" s="18"/>
     </row>
     <row r="20" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A20" s="6"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="20"/>
+      <c r="A20" s="4"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="18"/>
     </row>
     <row r="21" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A21" s="6"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="20"/>
+      <c r="A21" s="4"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="18"/>
     </row>
     <row r="22" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A22" s="6"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="20"/>
+      <c r="A22" s="4"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="18"/>
     </row>
     <row r="23" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A23" s="6"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="20"/>
+      <c r="A23" s="4"/>
+      <c r="B23" s="12"/>
+      <c r="C23" s="18"/>
     </row>
     <row r="24" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A24" s="6"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="20"/>
+      <c r="A24" s="4"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="18"/>
     </row>
     <row r="25" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A25" s="6"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="20"/>
+      <c r="A25" s="4"/>
+      <c r="B25" s="12"/>
+      <c r="C25" s="18"/>
     </row>
     <row r="26" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A26" s="7"/>
-      <c r="B26" s="21"/>
-      <c r="C26" s="23"/>
+      <c r="A26" s="5"/>
+      <c r="B26" s="19"/>
+      <c r="C26" s="21"/>
     </row>
     <row r="27" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A27" s="7"/>
-      <c r="B27" s="21"/>
-      <c r="C27" s="23"/>
+      <c r="A27" s="5"/>
+      <c r="B27" s="19"/>
+      <c r="C27" s="21"/>
     </row>
     <row r="28" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A28" s="7"/>
-      <c r="B28" s="21"/>
-      <c r="C28" s="23"/>
+      <c r="A28" s="5"/>
+      <c r="B28" s="19"/>
+      <c r="C28" s="21"/>
     </row>
     <row r="29" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A29" s="7"/>
-      <c r="B29" s="21"/>
-      <c r="C29" s="23"/>
+      <c r="A29" s="5"/>
+      <c r="B29" s="19"/>
+      <c r="C29" s="21"/>
     </row>
     <row r="30" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A30" s="7"/>
-      <c r="B30" s="21"/>
-      <c r="C30" s="23"/>
+      <c r="A30" s="5"/>
+      <c r="B30" s="19"/>
+      <c r="C30" s="21"/>
     </row>
     <row r="31" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A31" s="7"/>
-      <c r="B31" s="21"/>
-      <c r="C31" s="23"/>
+      <c r="A31" s="5"/>
+      <c r="B31" s="19"/>
+      <c r="C31" s="21"/>
     </row>
     <row r="32" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A32" s="8"/>
-      <c r="B32" s="22"/>
-      <c r="C32" s="24"/>
+      <c r="A32" s="6"/>
+      <c r="B32" s="20"/>
+      <c r="C32" s="22"/>
     </row>
     <row r="33" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A33" s="8"/>
-      <c r="B33" s="22"/>
-      <c r="C33" s="24"/>
+      <c r="A33" s="6"/>
+      <c r="B33" s="20"/>
+      <c r="C33" s="22"/>
     </row>
     <row r="34" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A34" s="8"/>
-      <c r="B34" s="22"/>
-      <c r="C34" s="24"/>
+      <c r="A34" s="6"/>
+      <c r="B34" s="20"/>
+      <c r="C34" s="22"/>
     </row>
     <row r="35" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A35" s="8"/>
-      <c r="B35" s="22"/>
-      <c r="C35" s="24"/>
+      <c r="A35" s="6"/>
+      <c r="B35" s="20"/>
+      <c r="C35" s="22"/>
     </row>
     <row r="36" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="37" spans="1:3" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/Dialogue.xlsx
+++ b/JsonConverter/ExcelFiles/Dialogue.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SunnyHoGaming\JsonConverter\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0916ffeaa849160d/문서/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D5C1B72-FB9F-4AE7-9B4A-0068CAFC4FEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="63" documentId="8_{597440D9-FF3C-4ACD-9BD1-E4D8E2E87309}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FC513FEC-A3D5-4EB2-9CEA-40C3BF6A613E}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table_Story" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="63">
   <si>
     <t>Id</t>
   </si>
@@ -58,85 +58,873 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
+    <t>혼자 남게 되었다</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>절망적이지만 나는 살아야만 한다</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>정신차리고 주변을 살펴보자</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Day1_002</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Day1_003</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>산소 공급기 또한 손상되었구나</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>서둘러 수리해보자</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Day1_005</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>정말 핵심 기능들이 많이 손상되었네</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Day1_007</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>탐사선 내부 온도도 불안정하다</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Day1_006</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Day1_004</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>전력이 모두 소진되기전에 수리하자</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>점점 지구와 멀어지고 있었다니</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>서둘러 항로 제어기를 수리하자</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Day1_010</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Day1_008</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Day1_009</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Day1_012</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Day1_013</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>가슴이 찢어질 것 같아... 산소 공급 장치가 어디 있지?!</t>
+  </si>
+  <si>
+    <t>가슴이 찢어질 것 같아... 산소 공급 장치가 어디 있지?!</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Day1_014</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Day1_015</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Day1_016</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Day1_017</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <t>Dialogue_Day1_011</t>
-  </si>
-  <si>
-    <t>Dialogue_Day1_012</t>
-  </si>
-  <si>
-    <t>혼자 남게 되었다</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>절망적이지만 나는 살아야만 한다</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>정신차리고 주변을 살펴보자</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dialogue_Day1_002</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dialogue_Day1_003</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>산소 공급기 또한 손상되었구나</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>서둘러 수리해보자</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dialogue_Day1_005</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>정말 핵심 기능들이 많이 손상되었네</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dialogue_Day1_007</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>탐사선 내부 온도도 불안정하다</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dialogue_Day1_006</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dialogue_Day1_004</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>전력이 모두 소진되기전에 수리하자</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>점점 지구와 멀어지고 있었다니</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>서둘러 항로 제어기를 수리하자</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dialogue_Day1_010</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dialogue_Day1_008</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dialogue_Day1_009</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Day2_001</t>
+  </si>
+  <si>
+    <t>헉... 헉... 숨이... 막혀온다…</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>아무래도 이건가 보군</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>후</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">... </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이제야</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>살</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>것</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>같군</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>산소</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>농도가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>안정되었어</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>전력이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>모두</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>소진되기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>전에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>항로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>제어기를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>서둘러</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수리하자</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>오늘은 이쯤에서 쉬도록 할까?</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>무사히 하루를 넘겼군</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Day2_002</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>바닥에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>무언가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>떨어져</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>뭐지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>?</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Day2_003</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Day2_004</t>
+  </si>
+  <si>
+    <t>동료가 남긴 기록이 앞으로의 생존에 도움이 될 것 같다. 잘 챙겨두자.</t>
+  </si>
+  <si>
+    <t>Dialogue_Day3_001</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Day4_001</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Day5_001</t>
+  </si>
+  <si>
+    <t>Dialogue_Day5_002</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Day5_003</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Day5_004</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이건</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">... </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>먼서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>떠난</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>동료가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>남긴</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>숨겨진</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>노트잖아</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>?</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>이녀석은 유용하게 쓸 수 있겠군</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Fixer? </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이번엔 뭘 가져온거지?</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>앞으로 잘 부탁한다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이건</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>... '</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>위성전화기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">'?! </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>도대체</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이걸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>어디서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>찾아온</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>거지?</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>당장 신호를 보내보자</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>치지직…치직…여기는..치지 지구본부..생존자 있습니까?</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -144,7 +932,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="9">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -168,6 +956,40 @@
       <sz val="8"/>
       <name val="돋움"/>
       <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <charset val="129"/>
     </font>
   </fonts>
@@ -266,7 +1088,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -277,9 +1099,6 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -295,7 +1114,6 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -312,10 +1130,17 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -331,6 +1156,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -535,21 +1364,21 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:C1000"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="31.85546875" customWidth="1"/>
-    <col min="2" max="2" width="42.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.28515625" customWidth="1"/>
+    <col min="1" max="1" width="31.88671875" customWidth="1"/>
+    <col min="2" max="2" width="42.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="9" t="s">
         <v>8</v>
       </c>
     </row>
@@ -557,10 +1386,10 @@
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="9" t="s">
         <v>6</v>
       </c>
     </row>
@@ -568,10 +1397,10 @@
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="10" t="s">
         <v>9</v>
       </c>
     </row>
@@ -579,217 +1408,298 @@
       <c r="A4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="15" t="s">
-        <v>15</v>
+      <c r="B4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15.75" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="15" t="s">
-        <v>16</v>
+      <c r="B5" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15.75" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="15"/>
+      <c r="B6" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="11"/>
     </row>
     <row r="7" spans="1:3" ht="15.75" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="11" t="s">
         <v>17</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15.75" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="16"/>
+        <v>17</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="12"/>
     </row>
     <row r="9" spans="1:3" ht="15.75" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" s="16" t="s">
         <v>21</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15.75" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="17"/>
+        <v>19</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="13"/>
     </row>
     <row r="11" spans="1:3" ht="15.75" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" s="17"/>
+        <v>27</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="13"/>
     </row>
     <row r="12" spans="1:3" ht="15.75" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B12" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="12" t="s">
         <v>26</v>
-      </c>
-      <c r="C12" s="16" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="15.75" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C13" s="15"/>
+        <v>26</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="11"/>
     </row>
     <row r="14" spans="1:3" ht="15.75" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B14" s="11"/>
-      <c r="C14" s="17"/>
+        <v>37</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="13"/>
     </row>
     <row r="15" spans="1:3" ht="15.75" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B15" s="11"/>
-      <c r="C15" s="17"/>
+        <v>29</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" s="17" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="16" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A16" s="4"/>
-      <c r="B16" s="12"/>
-      <c r="C16" s="18"/>
+      <c r="A16" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="17" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A17" s="4"/>
-      <c r="B17" s="12"/>
-      <c r="C17" s="18"/>
+      <c r="A17" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17" s="14"/>
     </row>
     <row r="18" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A18" s="4"/>
-      <c r="B18" s="12"/>
-      <c r="C18" s="18"/>
+      <c r="A18" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="C18" s="14"/>
     </row>
     <row r="19" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A19" s="4"/>
-      <c r="B19" s="12"/>
-      <c r="C19" s="18"/>
+      <c r="A19" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="C19" s="14"/>
     </row>
     <row r="20" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A20" s="4"/>
-      <c r="B20" s="12"/>
-      <c r="C20" s="18"/>
+      <c r="A20" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20" s="14"/>
     </row>
     <row r="21" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A21" s="4"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="18"/>
+      <c r="A21" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="C21" s="14"/>
     </row>
     <row r="22" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A22" s="4"/>
-      <c r="B22" s="12"/>
-      <c r="C22" s="18"/>
+      <c r="A22" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B22" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="C22" s="18" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="23" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A23" s="4"/>
-      <c r="B23" s="12"/>
-      <c r="C23" s="18"/>
+      <c r="A23" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="B23" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="C23" s="18" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="24" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A24" s="4"/>
-      <c r="B24" s="12"/>
-      <c r="C24" s="18"/>
+      <c r="A24" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="B24" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="C24" s="14"/>
     </row>
     <row r="25" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A25" s="4"/>
-      <c r="B25" s="12"/>
+      <c r="A25" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="B25" s="23" t="s">
+        <v>57</v>
+      </c>
       <c r="C25" s="18"/>
     </row>
     <row r="26" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A26" s="5"/>
-      <c r="B26" s="19"/>
-      <c r="C26" s="21"/>
+      <c r="A26" s="18"/>
+      <c r="B26" s="24"/>
+      <c r="C26" s="18"/>
     </row>
     <row r="27" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A27" s="5"/>
-      <c r="B27" s="19"/>
-      <c r="C27" s="21"/>
+      <c r="A27" s="18"/>
+      <c r="B27" s="23"/>
+      <c r="C27" s="18"/>
     </row>
     <row r="28" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A28" s="5"/>
-      <c r="B28" s="19"/>
-      <c r="C28" s="21"/>
+      <c r="A28" s="18"/>
+      <c r="B28" s="23"/>
+      <c r="C28" s="15"/>
     </row>
     <row r="29" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A29" s="5"/>
-      <c r="B29" s="19"/>
-      <c r="C29" s="21"/>
+      <c r="A29" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="B29" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="C29" s="18"/>
     </row>
     <row r="30" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A30" s="5"/>
-      <c r="B30" s="19"/>
-      <c r="C30" s="21"/>
+      <c r="A30" s="18"/>
+      <c r="B30" s="22"/>
+      <c r="C30" s="18"/>
     </row>
     <row r="31" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A31" s="5"/>
-      <c r="B31" s="19"/>
-      <c r="C31" s="21"/>
+      <c r="A31" s="18"/>
+      <c r="B31" s="23"/>
+      <c r="C31" s="18"/>
     </row>
     <row r="32" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A32" s="6"/>
-      <c r="B32" s="20"/>
-      <c r="C32" s="22"/>
+      <c r="A32" s="18"/>
+      <c r="B32" s="25"/>
+      <c r="C32" s="16"/>
     </row>
     <row r="33" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A33" s="6"/>
-      <c r="B33" s="20"/>
-      <c r="C33" s="22"/>
+      <c r="A33" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B33" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="C33" s="18" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="34" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A34" s="6"/>
-      <c r="B34" s="20"/>
-      <c r="C34" s="22"/>
+      <c r="A34" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="B34" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="C34" s="18" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="35" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A35" s="6"/>
-      <c r="B35" s="20"/>
-      <c r="C35" s="22"/>
-    </row>
-    <row r="36" spans="1:3" ht="15.75" customHeight="1"/>
+      <c r="A35" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="B35" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="C35" s="18" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A36" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="B36" s="24" t="s">
+        <v>62</v>
+      </c>
+    </row>
     <row r="37" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="38" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="39" spans="1:3" ht="15.75" customHeight="1"/>
@@ -1757,6 +2667,6 @@
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
-  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/Dialogue.xlsx
+++ b/JsonConverter/ExcelFiles/Dialogue.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0916ffeaa849160d/문서/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SunnyHoGaming\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="63" documentId="8_{597440D9-FF3C-4ACD-9BD1-E4D8E2E87309}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FC513FEC-A3D5-4EB2-9CEA-40C3BF6A613E}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5CB9572-17E3-4BCE-97A9-440AF00CDF67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table_Story" sheetId="1" r:id="rId1"/>
@@ -1031,7 +1031,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -1082,42 +1082,58 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1132,15 +1148,25 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1156,10 +1182,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1364,21 +1386,21 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:C1000"/>
-  <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="31.88671875" customWidth="1"/>
-    <col min="2" max="2" width="42.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.33203125" customWidth="1"/>
+    <col min="1" max="1" width="31.85546875" customWidth="1"/>
+    <col min="2" max="2" width="64.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="3" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1386,329 +1408,366 @@
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="12" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="4" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="11"/>
+      <c r="C6" s="4"/>
     </row>
     <row r="7" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="4" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="12"/>
+      <c r="C8" s="5"/>
     </row>
     <row r="9" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="5" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="13"/>
+      <c r="C10" s="6"/>
     </row>
     <row r="11" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="13"/>
+      <c r="C11" s="6"/>
     </row>
     <row r="12" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="5" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="11"/>
+      <c r="C13" s="4"/>
     </row>
     <row r="14" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="13"/>
+      <c r="C14" s="6"/>
     </row>
     <row r="15" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="C15" s="17" t="s">
+      <c r="C15" s="14" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A16" s="17" t="s">
+      <c r="A16" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="B16" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="17" t="s">
+      <c r="C16" s="14" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A17" s="17" t="s">
+      <c r="A17" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="B17" s="20" t="s">
+      <c r="B17" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="C17" s="14"/>
+      <c r="C17" s="7"/>
     </row>
     <row r="18" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A18" s="17" t="s">
+      <c r="A18" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="B18" s="21" t="s">
+      <c r="B18" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="C18" s="14"/>
+      <c r="C18" s="7"/>
     </row>
     <row r="19" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A19" s="17" t="s">
+      <c r="A19" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="B19" s="22" t="s">
+      <c r="B19" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="C19" s="14"/>
+      <c r="C19" s="7"/>
     </row>
     <row r="20" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A20" s="17" t="s">
+      <c r="A20" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="B20" s="20" t="s">
+      <c r="B20" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="C20" s="14"/>
+      <c r="C20" s="7"/>
     </row>
     <row r="21" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A21" s="17" t="s">
+      <c r="A21" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="20" t="s">
+      <c r="B21" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="C21" s="14"/>
+      <c r="C21" s="7"/>
     </row>
     <row r="22" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A22" s="18" t="s">
+      <c r="A22" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="B22" s="21" t="s">
+      <c r="B22" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="C22" s="18" t="s">
+      <c r="C22" s="15" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A23" s="18" t="s">
+      <c r="A23" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="B23" s="21" t="s">
+      <c r="B23" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="C23" s="18" t="s">
+      <c r="C23" s="15" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A24" s="18" t="s">
+      <c r="A24" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="B24" s="18" t="s">
+      <c r="B24" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="C24" s="14"/>
+      <c r="C24" s="7"/>
     </row>
     <row r="25" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A25" s="18" t="s">
+      <c r="A25" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="B25" s="23" t="s">
+      <c r="B25" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="C25" s="18"/>
+      <c r="C25" s="15"/>
     </row>
     <row r="26" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A26" s="18"/>
-      <c r="B26" s="24"/>
-      <c r="C26" s="18"/>
+      <c r="A26" s="15"/>
+      <c r="B26" s="20"/>
+      <c r="C26" s="15"/>
     </row>
     <row r="27" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A27" s="18"/>
-      <c r="B27" s="23"/>
-      <c r="C27" s="18"/>
+      <c r="A27" s="15"/>
+      <c r="B27" s="19"/>
+      <c r="C27" s="15"/>
     </row>
     <row r="28" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A28" s="18"/>
-      <c r="B28" s="23"/>
-      <c r="C28" s="15"/>
+      <c r="A28" s="15"/>
+      <c r="B28" s="19"/>
+      <c r="C28" s="8"/>
     </row>
     <row r="29" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A29" s="18" t="s">
+      <c r="A29" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="B29" s="23" t="s">
+      <c r="B29" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="C29" s="18"/>
+      <c r="C29" s="15"/>
     </row>
     <row r="30" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A30" s="18"/>
-      <c r="B30" s="22"/>
-      <c r="C30" s="18"/>
+      <c r="A30" s="15"/>
+      <c r="B30" s="18"/>
+      <c r="C30" s="15"/>
     </row>
     <row r="31" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A31" s="18"/>
-      <c r="B31" s="23"/>
-      <c r="C31" s="18"/>
+      <c r="A31" s="15"/>
+      <c r="B31" s="19"/>
+      <c r="C31" s="15"/>
     </row>
     <row r="32" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A32" s="18"/>
-      <c r="B32" s="25"/>
-      <c r="C32" s="16"/>
+      <c r="A32" s="15"/>
+      <c r="B32" s="21"/>
+      <c r="C32" s="9"/>
     </row>
     <row r="33" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A33" s="18" t="s">
+      <c r="A33" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="B33" s="18" t="s">
+      <c r="B33" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="C33" s="18" t="s">
+      <c r="C33" s="15" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A34" s="18" t="s">
+      <c r="A34" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="B34" s="21" t="s">
+      <c r="B34" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="C34" s="18" t="s">
+      <c r="C34" s="15" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A35" s="18" t="s">
+      <c r="A35" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="B35" s="25" t="s">
+      <c r="B35" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="C35" s="18" t="s">
+      <c r="C35" s="15" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A36" s="18" t="s">
+      <c r="A36" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="B36" s="24" t="s">
+      <c r="B36" s="20" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="38" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="39" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="40" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="41" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="42" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="43" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="44" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="45" spans="1:3" ht="15.75" customHeight="1"/>
+      <c r="C36" s="22"/>
+    </row>
+    <row r="37" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A37" s="22"/>
+      <c r="B37" s="22"/>
+      <c r="C37" s="22"/>
+    </row>
+    <row r="38" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A38" s="22"/>
+      <c r="B38" s="22"/>
+      <c r="C38" s="22"/>
+    </row>
+    <row r="39" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A39" s="22"/>
+      <c r="B39" s="22"/>
+      <c r="C39" s="22"/>
+    </row>
+    <row r="40" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A40" s="22"/>
+      <c r="B40" s="22"/>
+      <c r="C40" s="22"/>
+    </row>
+    <row r="41" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A41" s="22"/>
+      <c r="B41" s="22"/>
+      <c r="C41" s="22"/>
+    </row>
+    <row r="42" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A42" s="22"/>
+      <c r="B42" s="22"/>
+      <c r="C42" s="22"/>
+    </row>
+    <row r="43" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A43" s="22"/>
+      <c r="B43" s="22"/>
+      <c r="C43" s="22"/>
+    </row>
+    <row r="44" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A44" s="22"/>
+      <c r="B44" s="22"/>
+      <c r="C44" s="22"/>
+    </row>
+    <row r="45" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A45" s="22"/>
+      <c r="B45" s="22"/>
+      <c r="C45" s="22"/>
+    </row>
     <row r="46" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="47" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="48" spans="1:3" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/Dialogue.xlsx
+++ b/JsonConverter/ExcelFiles/Dialogue.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SunnyHoGaming\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5CB9572-17E3-4BCE-97A9-440AF00CDF67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C646C48-B6C5-4563-AABC-650E6DF7532B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="51">
   <si>
     <t>Id</t>
   </si>
@@ -138,498 +138,61 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Dialogue_Day1_013</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>가슴이 찢어질 것 같아... 산소 공급 장치가 어디 있지?!</t>
-  </si>
-  <si>
-    <t>가슴이 찢어질 것 같아... 산소 공급 장치가 어디 있지?!</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dialogue_Day1_014</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dialogue_Day1_015</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dialogue_Day1_016</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dialogue_Day1_017</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>Dialogue_Day1_011</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Dialogue_Day2_001</t>
-  </si>
-  <si>
-    <t>헉... 헉... 숨이... 막혀온다…</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>아무래도 이건가 보군</t>
+    <t>Dialogue_Day2_003</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Day2_004</t>
+  </si>
+  <si>
+    <t>Dialogue_Day3_001</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Day4_001</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Day5_001</t>
+  </si>
+  <si>
+    <t>Dialogue_Day5_002</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Day5_003</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Day5_004</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>이녀석은 유용하게 쓸 수 있겠군</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>후</t>
+      <t xml:space="preserve">Fixer? </t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
         <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">... </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>이제야</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>살</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>것</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>같군</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>산소</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>농도가</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>안정되었어</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
         <rFont val="맑은 고딕"/>
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t>전력이</t>
+      <t>이번엔 뭘 가져온거지?</t>
     </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>모두</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>소진되기</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>전에</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>항로</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>제어기를</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>서둘러</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>수리하자</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>오늘은 이쯤에서 쉬도록 할까?</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>무사히 하루를 넘겼군</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dialogue_Day2_002</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>바닥에</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>무언가</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>떨어져</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>있다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>이게</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>뭐지</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>?</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dialogue_Day2_003</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dialogue_Day2_004</t>
-  </si>
-  <si>
-    <t>동료가 남긴 기록이 앞으로의 생존에 도움이 될 것 같다. 잘 챙겨두자.</t>
-  </si>
-  <si>
-    <t>Dialogue_Day3_001</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dialogue_Day4_001</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dialogue_Day5_001</t>
-  </si>
-  <si>
-    <t>Dialogue_Day5_002</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dialogue_Day5_003</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dialogue_Day5_004</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>앞으로 잘 부탁한다.</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -650,166 +213,6 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">... </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>먼서</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>떠난</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>동료가</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>남긴</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>숨겨진</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>노트잖아</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>?</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>이녀석은 유용하게 쓸 수 있겠군</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Fixer? </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>이번엔 뭘 가져온거지?</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>앞으로 잘 부탁한다.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>이건</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
       <t>... '</t>
     </r>
     <r>
@@ -925,6 +328,30 @@
   </si>
   <si>
     <t>치지직…치직…여기는..치지 지구본부..생존자 있습니까?</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>정말 상황이 안좋지만 내일도 생존하려면 잠을 자야한다</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>하루 일과를 잘 마무리하고 적절한 시간에 잠에 들자</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Day2_002</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Day2_001</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>이런 장비들이 있었다니 잘만 사용하면 유용하겠어</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">그저 창고라고 생각했는데 </t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1385,7 +812,7 @@
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C1000"/>
+  <dimension ref="A1:C995"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="31.85546875" customWidth="1"/>
@@ -1528,199 +955,169 @@
     </row>
     <row r="14" spans="1:3" ht="15.75" customHeight="1">
       <c r="A14" s="4" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C14" s="6"/>
+        <v>45</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="15" spans="1:3" ht="15.75" customHeight="1">
       <c r="A15" s="4" t="s">
         <v>29</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="C15" s="14" t="s">
-        <v>30</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="C15" s="14"/>
     </row>
     <row r="16" spans="1:3" ht="15.75" customHeight="1">
       <c r="A16" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="B16" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="C16" s="7"/>
+    </row>
+    <row r="17" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A17" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="C17" s="15"/>
+    </row>
+    <row r="18" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A18" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="14" t="s">
+      <c r="B18" s="17"/>
+      <c r="C18" s="15"/>
+    </row>
+    <row r="19" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A19" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19" s="15"/>
+      <c r="C19" s="7"/>
+    </row>
+    <row r="20" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A20" s="15" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A17" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="B17" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="C17" s="7"/>
-    </row>
-    <row r="18" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A18" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="C18" s="7"/>
-    </row>
-    <row r="19" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A19" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="B19" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="C19" s="7"/>
-    </row>
-    <row r="20" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A20" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="B20" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="C20" s="7"/>
+      <c r="B20" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" s="15"/>
     </row>
     <row r="21" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A21" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="B21" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="C21" s="7"/>
+      <c r="A21" s="15"/>
+      <c r="B21" s="20"/>
+      <c r="C21" s="15"/>
     </row>
     <row r="22" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A22" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="B22" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="C22" s="15" t="s">
-        <v>47</v>
-      </c>
+      <c r="A22" s="15"/>
+      <c r="B22" s="19"/>
+      <c r="C22" s="15"/>
     </row>
     <row r="23" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A23" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="B23" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="C23" s="15" t="s">
-        <v>48</v>
-      </c>
+      <c r="A23" s="15"/>
+      <c r="B23" s="19"/>
+      <c r="C23" s="8"/>
     </row>
     <row r="24" spans="1:3" ht="15.75" customHeight="1">
       <c r="A24" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="B24" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="C24" s="7"/>
+        <v>34</v>
+      </c>
+      <c r="B24" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="C24" s="15"/>
     </row>
     <row r="25" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A25" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="B25" s="19" t="s">
-        <v>57</v>
-      </c>
+      <c r="A25" s="15"/>
+      <c r="B25" s="18"/>
       <c r="C25" s="15"/>
     </row>
     <row r="26" spans="1:3" ht="15.75" customHeight="1">
       <c r="A26" s="15"/>
-      <c r="B26" s="20"/>
+      <c r="B26" s="19"/>
       <c r="C26" s="15"/>
     </row>
     <row r="27" spans="1:3" ht="15.75" customHeight="1">
       <c r="A27" s="15"/>
-      <c r="B27" s="19"/>
-      <c r="C27" s="15"/>
+      <c r="B27" s="21"/>
+      <c r="C27" s="9"/>
     </row>
     <row r="28" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A28" s="15"/>
-      <c r="B28" s="19"/>
-      <c r="C28" s="8"/>
+      <c r="A28" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="29" spans="1:3" ht="15.75" customHeight="1">
       <c r="A29" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="B29" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="C29" s="15"/>
+        <v>36</v>
+      </c>
+      <c r="B29" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="C29" s="15" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="30" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A30" s="15"/>
-      <c r="B30" s="18"/>
-      <c r="C30" s="15"/>
+      <c r="A30" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="C30" s="15" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="31" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A31" s="15"/>
-      <c r="B31" s="19"/>
-      <c r="C31" s="15"/>
+      <c r="A31" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="C31" s="22"/>
     </row>
     <row r="32" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A32" s="15"/>
-      <c r="B32" s="21"/>
-      <c r="C32" s="9"/>
+      <c r="A32" s="22"/>
+      <c r="B32" s="22"/>
+      <c r="C32" s="22"/>
     </row>
     <row r="33" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A33" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="B33" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="C33" s="15" t="s">
-        <v>53</v>
-      </c>
+      <c r="A33" s="22"/>
+      <c r="B33" s="22"/>
+      <c r="C33" s="22"/>
     </row>
     <row r="34" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A34" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="B34" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="C34" s="15" t="s">
-        <v>54</v>
-      </c>
+      <c r="A34" s="22"/>
+      <c r="B34" s="22"/>
+      <c r="C34" s="22"/>
     </row>
     <row r="35" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A35" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="B35" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="C35" s="15" t="s">
-        <v>55</v>
-      </c>
+      <c r="A35" s="22"/>
+      <c r="B35" s="22"/>
+      <c r="C35" s="22"/>
     </row>
     <row r="36" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A36" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="B36" s="20" t="s">
-        <v>62</v>
-      </c>
+      <c r="A36" s="22"/>
+      <c r="B36" s="22"/>
       <c r="C36" s="22"/>
     </row>
     <row r="37" spans="1:3" ht="15.75" customHeight="1">
@@ -1743,31 +1140,11 @@
       <c r="B40" s="22"/>
       <c r="C40" s="22"/>
     </row>
-    <row r="41" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A41" s="22"/>
-      <c r="B41" s="22"/>
-      <c r="C41" s="22"/>
-    </row>
-    <row r="42" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A42" s="22"/>
-      <c r="B42" s="22"/>
-      <c r="C42" s="22"/>
-    </row>
-    <row r="43" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A43" s="22"/>
-      <c r="B43" s="22"/>
-      <c r="C43" s="22"/>
-    </row>
-    <row r="44" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A44" s="22"/>
-      <c r="B44" s="22"/>
-      <c r="C44" s="22"/>
-    </row>
-    <row r="45" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A45" s="22"/>
-      <c r="B45" s="22"/>
-      <c r="C45" s="22"/>
-    </row>
+    <row r="41" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="42" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="43" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="44" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="45" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="46" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="47" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="48" spans="1:3" ht="15.75" customHeight="1"/>
@@ -2718,11 +2095,6 @@
     <row r="993" ht="15.75" customHeight="1"/>
     <row r="994" ht="15.75" customHeight="1"/>
     <row r="995" ht="15.75" customHeight="1"/>
-    <row r="996" ht="15.75" customHeight="1"/>
-    <row r="997" ht="15.75" customHeight="1"/>
-    <row r="998" ht="15.75" customHeight="1"/>
-    <row r="999" ht="15.75" customHeight="1"/>
-    <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>

--- a/JsonConverter/ExcelFiles/Dialogue.xlsx
+++ b/JsonConverter/ExcelFiles/Dialogue.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SunnyHoGaming\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C646C48-B6C5-4563-AABC-650E6DF7532B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56FD3395-90DE-42DA-8A1F-D8A23A89103B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="121">
   <si>
     <t>Id</t>
   </si>
@@ -146,9 +146,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Dialogue_Day2_004</t>
-  </si>
-  <si>
     <t>Dialogue_Day3_001</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -157,9 +154,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Dialogue_Day5_001</t>
-  </si>
-  <si>
     <t>Dialogue_Day5_002</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -172,27 +166,27 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>이녀석은 유용하게 쓸 수 있겠군</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Fixer? </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>이번엔 뭘 가져온거지?</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>앞으로 잘 부탁한다.</t>
+    <t>정말 상황이 안좋지만 내일도 생존하려면 잠을 자야한다</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>하루 일과를 잘 마무리하고 적절한 시간에 잠에 들자</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Day2_002</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Day2_001</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>이런 장비들이 있었다니 잘만 사용하면 유용하겠어</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">그저 창고라고 생각했는데 </t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -204,52 +198,14 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>이건</t>
+      <t>이런</t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>... '</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
         <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>위성전화기</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">'?! </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>도대체</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -261,17 +217,265 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>이걸</t>
+      <t>공간들이 있을줄이야</t>
     </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Day2_004</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Day2_005</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>서둘러 해금방으로 가보자</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">비밀번호? </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Day2_006</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>분명 어디선가 단서가 있을 것이다</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Day2_007</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>이 친구들이 기능 수리를 할 수 있다니</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Day2_008</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>생존에 더 도움이 되겠어</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>마침 수리할 수 있는 재료들도 부족했는데</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Day3_002</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>정말 다행이야. 새로운 재료 수급 루트가 생겼어</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Day3_003</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>오늘도 효율적인 스케줄링을 해보자</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>식당 붕괴로 인해 밥은 못먹게 될줄 알았는데</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>한 시름 덜겠군</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Day4_002</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>픽서 너가 없었다면 난 진작에 죽었을거야</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>오늘도 함께 생존하자 얘들아</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Day4_004</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Day4_003</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Day5_001</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>위성 전화기를 찾아오다니</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>덕분에 지구에 구조 요청을 할 수 있겠어</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>그런데 뭔가를 입력해야 하는데</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>단서를 찾아보자</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Day5_008</t>
+  </si>
+  <si>
+    <t>Dialogue_Day5_009</t>
+  </si>
+  <si>
+    <t>Dialogue_Day5_010</t>
+  </si>
+  <si>
+    <t>Dialogue_Day5_011</t>
+  </si>
+  <si>
+    <t>Dialogue_Day5_012</t>
+  </si>
+  <si>
+    <t>Dialogue_Day5_013</t>
+  </si>
+  <si>
+    <t>…ㅇ..여..ㅇㅇ</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>….ㅕ.. 기느 …</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>??: 여기는 알파 알파 응답하라 써니호</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>여기는 써니호 현재 긴급 상황이다</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>??: 현황 보고 바랍니다</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>네 현재 소행성 충돌로 인한</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>저를 제외한 모든 인원이 사망하였고,</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>현재 탐사선 또한 핵심 기능들의 손상으로</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>위기에 처했습니다</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Day5_014</t>
+  </si>
+  <si>
+    <t>구조 요청 바랍니다</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Day5_015</t>
+  </si>
+  <si>
+    <t>Dialogue_Day5_016</t>
+  </si>
+  <si>
+    <t>??: 상황 접수 받았고, 구조대 보내겠습니다</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>??: 그때까지 부디 생존하여 주십시오</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Day5_017</t>
+  </si>
+  <si>
+    <t>Dialogue_Day5_018</t>
+  </si>
+  <si>
+    <t>Dialogue_Day5_019</t>
+  </si>
+  <si>
+    <t>혹시 시간은 얼마나 걸릴까요?</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>??: 30시간부터 최대 60시간까지 걸릴듯 합니다</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>알겠습니다. 응답 감사합니다</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Day5_020</t>
+  </si>
+  <si>
+    <t>지구와 연락 할 수 있어 정말 다행이다</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Day5_021</t>
+  </si>
+  <si>
+    <t>조금만 기다리면 사랑하는 가족들을 볼 수 있다</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Day5_005</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Day5_006</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Day5_007</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Day5_022</t>
+  </si>
+  <si>
+    <t>Dialogue_Day5_021</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Day6_001</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>핵심 기능들이 전보다 더 손상이 심해졌어</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Day6_003</t>
+  </si>
+  <si>
+    <t>Dialogue_Day6_004</t>
+  </si>
+  <si>
+    <t>Dialogue_Day6_006</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -280,78 +484,50 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>어디서</t>
+      <t>구조</t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
         <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
+        <rFont val="돋움"/>
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>찾아온</t>
+      <t>대가 오기전까진 버텨야해</t>
     </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>거지?</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>당장 신호를 보내보자</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>치지직…치직…여기는..치지 지구본부..생존자 있습니까?</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>정말 상황이 안좋지만 내일도 생존하려면 잠을 자야한다</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>하루 일과를 잘 마무리하고 적절한 시간에 잠에 들자</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dialogue_Day2_002</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dialogue_Day2_001</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>이런 장비들이 있었다니 잘만 사용하면 유용하겠어</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">그저 창고라고 생각했는데 </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>서둘러 수리하자</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Day6_002</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>수리도의 수치가 너무 빠르게 떨어진다</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>이대로는 안되겠어</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Day6_005</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>아… 아직은 안되는데</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>여기까진가…가족들을 볼 수 없을거 같군</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Day6_007</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -359,7 +535,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -416,7 +592,13 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="돋움"/>
+      <family val="3"/>
       <charset val="129"/>
     </font>
   </fonts>
@@ -458,7 +640,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -546,13 +728,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -589,11 +782,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -812,7 +1006,7 @@
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C995"/>
+  <dimension ref="A1:C1019"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="31.85546875" customWidth="1"/>
@@ -958,7 +1152,7 @@
         <v>30</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>29</v>
@@ -969,201 +1163,491 @@
         <v>29</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C15" s="14"/>
     </row>
     <row r="16" spans="1:3" ht="15.75" customHeight="1">
       <c r="A16" s="14" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="C16" s="7"/>
     </row>
     <row r="17" spans="1:3" ht="15.75" customHeight="1">
       <c r="A17" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="B17" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="C17" s="15"/>
+        <v>39</v>
+      </c>
+      <c r="B17" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="18" spans="1:3" ht="15.75" customHeight="1">
       <c r="A18" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="B18" s="17"/>
-      <c r="C18" s="15"/>
+      <c r="B18" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="19" spans="1:3" ht="15.75" customHeight="1">
       <c r="A19" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="B19" s="15"/>
+        <v>44</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>46</v>
+      </c>
       <c r="C19" s="7"/>
     </row>
     <row r="20" spans="1:3" ht="15.75" customHeight="1">
       <c r="A20" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="B20" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="C20" s="15"/>
+        <v>45</v>
+      </c>
+      <c r="B20" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="21" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A21" s="15"/>
-      <c r="B21" s="20"/>
+      <c r="A21" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="B21" s="19" t="s">
+        <v>49</v>
+      </c>
       <c r="C21" s="15"/>
     </row>
     <row r="22" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A22" s="15"/>
-      <c r="B22" s="19"/>
-      <c r="C22" s="15"/>
+      <c r="A22" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="B22" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="C22" s="15" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="23" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A23" s="15"/>
-      <c r="B23" s="19"/>
+      <c r="A23" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="B23" s="18" t="s">
+        <v>53</v>
+      </c>
       <c r="C23" s="8"/>
     </row>
     <row r="24" spans="1:3" ht="15.75" customHeight="1">
       <c r="A24" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="B24" s="19" t="s">
-        <v>41</v>
+        <v>32</v>
+      </c>
+      <c r="B24" s="18" t="s">
+        <v>54</v>
       </c>
       <c r="C24" s="15"/>
     </row>
     <row r="25" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A25" s="15"/>
-      <c r="B25" s="18"/>
-      <c r="C25" s="15"/>
+      <c r="A25" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="26" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A26" s="15"/>
-      <c r="B26" s="19"/>
+      <c r="A26" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="B26" s="18" t="s">
+        <v>58</v>
+      </c>
       <c r="C26" s="15"/>
     </row>
     <row r="27" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A27" s="15"/>
-      <c r="B27" s="21"/>
-      <c r="C27" s="9"/>
+      <c r="A27" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="B27" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="C27" s="22" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="28" spans="1:3" ht="15.75" customHeight="1">
       <c r="A28" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="B28" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="C28" s="15" t="s">
-        <v>36</v>
+        <v>61</v>
+      </c>
+      <c r="B28" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="C28" s="22" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="15.75" customHeight="1">
       <c r="A29" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="B29" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="C29" s="15" t="s">
-        <v>37</v>
+        <v>65</v>
+      </c>
+      <c r="B29" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="C29" s="22" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="15.75" customHeight="1">
       <c r="A30" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="B30" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="C30" s="15" t="s">
-        <v>38</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="B30" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="C30" s="9"/>
     </row>
     <row r="31" spans="1:3" ht="15.75" customHeight="1">
       <c r="A31" s="15" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="B31" s="20" t="s">
-        <v>44</v>
-      </c>
-      <c r="C31" s="22"/>
+        <v>67</v>
+      </c>
+      <c r="C31" s="22" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="32" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A32" s="22"/>
-      <c r="B32" s="22"/>
-      <c r="C32" s="22"/>
+      <c r="A32" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="B32" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="C32" s="22" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="33" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A33" s="22"/>
-      <c r="B33" s="22"/>
-      <c r="C33" s="22"/>
+      <c r="A33" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="B33" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="C33" s="22" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="34" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A34" s="22"/>
-      <c r="B34" s="22"/>
-      <c r="C34" s="22"/>
+      <c r="A34" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="B34" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="C34" s="9"/>
     </row>
     <row r="35" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A35" s="22"/>
-      <c r="B35" s="22"/>
-      <c r="C35" s="22"/>
+      <c r="A35" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="B35" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="C35" s="22" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="36" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A36" s="22"/>
-      <c r="B36" s="22"/>
-      <c r="C36" s="22"/>
+      <c r="A36" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="B36" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="C36" s="22" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="37" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A37" s="22"/>
-      <c r="B37" s="22"/>
-      <c r="C37" s="22"/>
+      <c r="A37" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="B37" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="C37" s="22" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="38" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A38" s="22"/>
-      <c r="B38" s="22"/>
-      <c r="C38" s="22"/>
+      <c r="A38" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="B38" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="C38" s="22" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="39" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A39" s="22"/>
-      <c r="B39" s="22"/>
-      <c r="C39" s="22"/>
+      <c r="A39" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="B39" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="C39" s="22" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="40" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A40" s="22"/>
-      <c r="B40" s="22"/>
-      <c r="C40" s="22"/>
-    </row>
-    <row r="41" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="42" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="43" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="44" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="45" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="46" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="47" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="48" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="49" ht="15.75" customHeight="1"/>
-    <row r="50" ht="15.75" customHeight="1"/>
-    <row r="51" ht="15.75" customHeight="1"/>
-    <row r="52" ht="15.75" customHeight="1"/>
-    <row r="53" ht="15.75" customHeight="1"/>
-    <row r="54" ht="15.75" customHeight="1"/>
-    <row r="55" ht="15.75" customHeight="1"/>
-    <row r="56" ht="15.75" customHeight="1"/>
-    <row r="57" ht="15.75" customHeight="1"/>
-    <row r="58" ht="15.75" customHeight="1"/>
-    <row r="59" ht="15.75" customHeight="1"/>
-    <row r="60" ht="15.75" customHeight="1"/>
-    <row r="61" ht="15.75" customHeight="1"/>
-    <row r="62" ht="15.75" customHeight="1"/>
-    <row r="63" ht="15.75" customHeight="1"/>
-    <row r="64" ht="15.75" customHeight="1"/>
+      <c r="A40" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B40" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="C40" s="22" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A41" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="B41" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="C41" s="22" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A42" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="B42" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="C42" s="22" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A43" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="B43" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="C43" s="22" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A44" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="B44" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="C44" s="22" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A45" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="B45" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="C45" s="22" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A46" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="B46" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="C46" s="22" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A47" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="B47" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="C47" s="22" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A48" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="B48" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="C48" s="22" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A49" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="B49" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="C49" s="22" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A50" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="B50" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="C50" s="22" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A51" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="B51" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="C51" s="22" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A52" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="B52" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="C52" s="15" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A53" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="B53" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="C53" s="15" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A54" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="B54" s="20" t="s">
+        <v>113</v>
+      </c>
+      <c r="C54" s="15"/>
+    </row>
+    <row r="55" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A55" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="B55" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="C55" s="15" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A56" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="B56" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="C56" s="21"/>
+    </row>
+    <row r="57" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A57" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="B57" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="C57" s="15" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A58" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="B58" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="C58" s="21"/>
+    </row>
+    <row r="59" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A59" s="21"/>
+      <c r="B59" s="21"/>
+      <c r="C59" s="21"/>
+    </row>
+    <row r="60" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A60" s="21"/>
+      <c r="B60" s="21"/>
+      <c r="C60" s="21"/>
+    </row>
+    <row r="61" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A61" s="21"/>
+      <c r="B61" s="21"/>
+      <c r="C61" s="21"/>
+    </row>
+    <row r="62" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A62" s="21"/>
+      <c r="B62" s="21"/>
+      <c r="C62" s="21"/>
+    </row>
+    <row r="63" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A63" s="21"/>
+      <c r="B63" s="21"/>
+      <c r="C63" s="21"/>
+    </row>
+    <row r="64" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A64" s="21"/>
+      <c r="B64" s="21"/>
+      <c r="C64" s="21"/>
+    </row>
     <row r="65" ht="15.75" customHeight="1"/>
     <row r="66" ht="15.75" customHeight="1"/>
     <row r="67" ht="15.75" customHeight="1"/>
@@ -2095,6 +2579,30 @@
     <row r="993" ht="15.75" customHeight="1"/>
     <row r="994" ht="15.75" customHeight="1"/>
     <row r="995" ht="15.75" customHeight="1"/>
+    <row r="996" ht="15.75" customHeight="1"/>
+    <row r="997" ht="15.75" customHeight="1"/>
+    <row r="998" ht="15.75" customHeight="1"/>
+    <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="1001" ht="15.75" customHeight="1"/>
+    <row r="1002" ht="15.75" customHeight="1"/>
+    <row r="1003" ht="15.75" customHeight="1"/>
+    <row r="1004" ht="15.75" customHeight="1"/>
+    <row r="1005" ht="15.75" customHeight="1"/>
+    <row r="1006" ht="15.75" customHeight="1"/>
+    <row r="1007" ht="15.75" customHeight="1"/>
+    <row r="1008" ht="15.75" customHeight="1"/>
+    <row r="1009" ht="15.75" customHeight="1"/>
+    <row r="1010" ht="15.75" customHeight="1"/>
+    <row r="1011" ht="15.75" customHeight="1"/>
+    <row r="1012" ht="15.75" customHeight="1"/>
+    <row r="1013" ht="15.75" customHeight="1"/>
+    <row r="1014" ht="15.75" customHeight="1"/>
+    <row r="1015" ht="15.75" customHeight="1"/>
+    <row r="1016" ht="15.75" customHeight="1"/>
+    <row r="1017" ht="15.75" customHeight="1"/>
+    <row r="1018" ht="15.75" customHeight="1"/>
+    <row r="1019" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>

--- a/JsonConverter/ExcelFiles/Dialogue.xlsx
+++ b/JsonConverter/ExcelFiles/Dialogue.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56FD3395-90DE-42DA-8A1F-D8A23A89103B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28260" yWindow="1635" windowWidth="28185" windowHeight="12795" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table_Story" sheetId="1" r:id="rId1"/>
@@ -787,7 +787,7 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>

--- a/JsonConverter/ExcelFiles/Dialogue.xlsx
+++ b/JsonConverter/ExcelFiles/Dialogue.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SunnyHoGaming\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56FD3395-90DE-42DA-8A1F-D8A23A89103B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{308B9BD2-11A8-416D-9875-9F4B411B5809}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28260" yWindow="1635" windowWidth="28185" windowHeight="12795" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table_Story" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="137">
   <si>
     <t>Id</t>
   </si>
@@ -473,9 +473,6 @@
     <t>Dialogue_Day6_004</t>
   </si>
   <si>
-    <t>Dialogue_Day6_006</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -519,15 +516,75 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>아… 아직은 안되는데</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>여기까진가…가족들을 볼 수 없을거 같군</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dialogue_Day6_007</t>
+    <t>Dialogue_Ending_001</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>그렇게 픽서들과 함께 구조되었고</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>안전하게 지구로 돌아올 수 있었다</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>뒤늦게 우리의 탐사선을 모니터링하던 요원에 말에 의하면</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">소행성 충돌이라고 단정했었던것은 </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>실제로 우리의 탐사선 근처에는 소행성의 행적이</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>단 1도 발견되지 않았다고 보고했다</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">그렇다는건 우리를 덮쳤던것은 </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>소행성이 아닌 결국엔 우리가 치우러 갔던 쓰레기 더미일 가능성이 높다</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>자연은 언제나 그렇듯 우리에게 위험 신호를 준다</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>언젠가는 부메랑처럼 모두 돌아오게 될것이다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Ending_003</t>
+  </si>
+  <si>
+    <t>Dialogue_Ending_004</t>
+  </si>
+  <si>
+    <t>Dialogue_Ending_005</t>
+  </si>
+  <si>
+    <t>Dialogue_Ending_006</t>
+  </si>
+  <si>
+    <t>Dialogue_Ending_007</t>
+  </si>
+  <si>
+    <t>Dialogue_Ending_008</t>
+  </si>
+  <si>
+    <t>Dialogue_Ending_009</t>
+  </si>
+  <si>
+    <t>Dialogue_Ending_010</t>
+  </si>
+  <si>
+    <t>Dialogue_Ending_002</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -745,7 +802,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -788,6 +845,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1555,15 +1613,15 @@
         <v>108</v>
       </c>
       <c r="C52" s="15" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="15.75" customHeight="1">
       <c r="A53" s="15" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B53" s="17" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C53" s="15" t="s">
         <v>109</v>
@@ -1574,7 +1632,7 @@
         <v>109</v>
       </c>
       <c r="B54" s="20" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C54" s="15"/>
     </row>
@@ -1583,87 +1641,142 @@
         <v>110</v>
       </c>
       <c r="B55" s="19" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C55" s="15" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="56" spans="1:3" ht="15.75" customHeight="1">
       <c r="A56" s="15" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B56" s="19" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C56" s="21"/>
     </row>
     <row r="57" spans="1:3" ht="15.75" customHeight="1">
       <c r="A57" s="15" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B57" s="23" t="s">
         <v>118</v>
       </c>
       <c r="C57" s="15" t="s">
-        <v>120</v>
+        <v>136</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="15.75" customHeight="1">
       <c r="A58" s="15" t="s">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="B58" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="C58" s="21"/>
+      <c r="C58" s="15" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="59" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A59" s="21"/>
-      <c r="B59" s="21"/>
-      <c r="C59" s="21"/>
+      <c r="A59" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="B59" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="C59" s="15" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="60" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A60" s="21"/>
-      <c r="B60" s="21"/>
-      <c r="C60" s="21"/>
+      <c r="A60" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="B60" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="C60" s="15" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="61" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A61" s="21"/>
-      <c r="B61" s="21"/>
-      <c r="C61" s="21"/>
+      <c r="A61" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="B61" s="19" t="s">
+        <v>122</v>
+      </c>
+      <c r="C61" s="15" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="62" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A62" s="21"/>
-      <c r="B62" s="21"/>
-      <c r="C62" s="21"/>
+      <c r="A62" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="B62" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="C62" s="15" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="63" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A63" s="21"/>
-      <c r="B63" s="21"/>
-      <c r="C63" s="21"/>
+      <c r="A63" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="B63" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="C63" s="15" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="64" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A64" s="21"/>
-      <c r="B64" s="21"/>
-      <c r="C64" s="21"/>
-    </row>
-    <row r="65" ht="15.75" customHeight="1"/>
-    <row r="66" ht="15.75" customHeight="1"/>
-    <row r="67" ht="15.75" customHeight="1"/>
-    <row r="68" ht="15.75" customHeight="1"/>
-    <row r="69" ht="15.75" customHeight="1"/>
-    <row r="70" ht="15.75" customHeight="1"/>
-    <row r="71" ht="15.75" customHeight="1"/>
-    <row r="72" ht="15.75" customHeight="1"/>
-    <row r="73" ht="15.75" customHeight="1"/>
-    <row r="74" ht="15.75" customHeight="1"/>
-    <row r="75" ht="15.75" customHeight="1"/>
-    <row r="76" ht="15.75" customHeight="1"/>
-    <row r="77" ht="15.75" customHeight="1"/>
-    <row r="78" ht="15.75" customHeight="1"/>
-    <row r="79" ht="15.75" customHeight="1"/>
-    <row r="80" ht="15.75" customHeight="1"/>
+      <c r="A64" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="B64" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="C64" s="15" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A65" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="B65" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="C65" s="15" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A66" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="B66" s="24" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="68" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="69" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="70" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="71" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="72" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="73" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="74" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="75" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="76" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="77" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="78" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="79" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="80" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="81" ht="15.75" customHeight="1"/>
     <row r="82" ht="15.75" customHeight="1"/>
     <row r="83" ht="15.75" customHeight="1"/>
